--- a/testbuild/StructureDefinition-vkp-Observation-NEWS2score.xlsx
+++ b/testbuild/StructureDefinition-vkp-Observation-NEWS2score.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.2</t>
+    <t>0.6.0-alpha</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T11:31:28+00:00</t>
+    <t>2026-10-02T06:31:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/testbuild/StructureDefinition-vkp-Observation-NEWS2score.xlsx
+++ b/testbuild/StructureDefinition-vkp-Observation-NEWS2score.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0-alpha</t>
+    <t>0.5.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T06:31:19+00:00</t>
+    <t>2026-10-02T08:56:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/testbuild/StructureDefinition-vkp-Observation-NEWS2score.xlsx
+++ b/testbuild/StructureDefinition-vkp-Observation-NEWS2score.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.2</t>
+    <t>0.6.0-alpha</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T08:56:17+00:00</t>
+    <t>2026-10-02T09:03:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1440,10 +1440,10 @@
     <t>FiveWs.actor</t>
   </si>
   <si>
-    <t>Observation.performer:author</t>
-  </si>
-  <si>
-    <t>author</t>
+    <t>Observation.performer:authorperson</t>
+  </si>
+  <si>
+    <t>authorperson</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(Practitioner|http://hl7.no/fhir/StructureDefinition/no-basis-Practitioner)
@@ -1453,7 +1453,7 @@
     <t>Reference to the author of the observation</t>
   </si>
   <si>
-    <t>Reference to the person, role or team that performed the observation, identified by Norwegian national id number (Fødselsnummer or DNR).
+    <t>Reference to the person that performed the observation, identified by Norwegian national id number (Fødselsnummer).
 A link to a resource representing the person or the group to whom the medication will be given.
 VKP always references a Practitioner Resource using a norwegian national id number (Fødselsnummer or DNR) in a logical identifier in the practitioner.identifier element.
 The Name of the practitioner should be given in the performer.display element.
@@ -1469,61 +1469,61 @@
 ~~~~</t>
   </si>
   <si>
-    <t>Observation.performer:author.id</t>
+    <t>Observation.performer:authorperson.id</t>
   </si>
   <si>
     <t>Observation.performer.id</t>
   </si>
   <si>
-    <t>Observation.performer:author.extension</t>
+    <t>Observation.performer:authorperson.extension</t>
   </si>
   <si>
     <t>Observation.performer.extension</t>
   </si>
   <si>
-    <t>Observation.performer:author.reference</t>
+    <t>Observation.performer:authorperson.reference</t>
   </si>
   <si>
     <t>Observation.performer.reference</t>
   </si>
   <si>
-    <t>Observation.performer:author.type</t>
+    <t>Observation.performer:authorperson.type</t>
   </si>
   <si>
     <t>Observation.performer.type</t>
   </si>
   <si>
-    <t>Observation.performer:author.identifier</t>
+    <t>Observation.performer:authorperson.identifier</t>
   </si>
   <si>
     <t>Observation.performer.identifier</t>
   </si>
   <si>
-    <t>Observation.performer:author.identifier.id</t>
+    <t>Observation.performer:authorperson.identifier.id</t>
   </si>
   <si>
     <t>Observation.performer.identifier.id</t>
   </si>
   <si>
-    <t>Observation.performer:author.identifier.extension</t>
+    <t>Observation.performer:authorperson.identifier.extension</t>
   </si>
   <si>
     <t>Observation.performer.identifier.extension</t>
   </si>
   <si>
-    <t>Observation.performer:author.identifier.use</t>
+    <t>Observation.performer:authorperson.identifier.use</t>
   </si>
   <si>
     <t>Observation.performer.identifier.use</t>
   </si>
   <si>
-    <t>Observation.performer:author.identifier.type</t>
+    <t>Observation.performer:authorperson.identifier.type</t>
   </si>
   <si>
     <t>Observation.performer.identifier.type</t>
   </si>
   <si>
-    <t>Observation.performer:author.identifier.system</t>
+    <t>Observation.performer:authorperson.identifier.system</t>
   </si>
   <si>
     <t>Observation.performer.identifier.system</t>
@@ -1532,25 +1532,25 @@
     <t>http://hl7.no/fhir/vkpobservation/ValueSet/vkp-performer-identifiers.valueset</t>
   </si>
   <si>
-    <t>Observation.performer:author.identifier.value</t>
+    <t>Observation.performer:authorperson.identifier.value</t>
   </si>
   <si>
     <t>Observation.performer.identifier.value</t>
   </si>
   <si>
-    <t>Observation.performer:author.identifier.period</t>
+    <t>Observation.performer:authorperson.identifier.period</t>
   </si>
   <si>
     <t>Observation.performer.identifier.period</t>
   </si>
   <si>
-    <t>Observation.performer:author.identifier.assigner</t>
+    <t>Observation.performer:authorperson.identifier.assigner</t>
   </si>
   <si>
     <t>Observation.performer.identifier.assigner</t>
   </si>
   <si>
-    <t>Observation.performer:author.display</t>
+    <t>Observation.performer:authorperson.display</t>
   </si>
   <si>
     <t>Observation.performer.display</t>
@@ -2472,9 +2472,9 @@
   <dimension ref="A1:AP123"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="44.95703125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="45.72265625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="11.4609375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>

--- a/testbuild/StructureDefinition-vkp-Observation-NEWS2score.xlsx
+++ b/testbuild/StructureDefinition-vkp-Observation-NEWS2score.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T09:03:30+00:00</t>
+    <t>2026-10-02T10:19:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1453,9 +1453,9 @@
     <t>Reference to the author of the observation</t>
   </si>
   <si>
-    <t>Reference to the person that performed the observation, identified by Norwegian national id number (Fødselsnummer).
+    <t>Reference to the person that performed the observation. The person is identified by Norwegian national id number (Fødselsnummer).
 A link to a resource representing the person or the group to whom the medication will be given.
-VKP always references a Practitioner Resource using a norwegian national id number (Fødselsnummer or DNR) in a logical identifier in the practitioner.identifier element.
+VKP always references a Practitioner Resource using a norwegian national id number (Fødselsnummer) in a logical identifier in the practitioner.identifier element.
 The Name of the practitioner should be given in the performer.display element.
 Example:
 ~~~~

--- a/testbuild/StructureDefinition-vkp-Observation-NEWS2score.xlsx
+++ b/testbuild/StructureDefinition-vkp-Observation-NEWS2score.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T10:19:39+00:00</t>
+    <t>2026-10-02T10:27:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
